--- a/frontend-vue/public/teste-clientes.xlsx
+++ b/frontend-vue/public/teste-clientes.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -411,6 +411,7 @@
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,6 +445,9 @@
       <c r="J1" t="str">
         <v>uf</v>
       </c>
+      <c r="K1" t="str">
+        <v>email</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -476,6 +480,9 @@
       <c r="J2" t="str">
         <v>sp</v>
       </c>
+      <c r="K2" t="str">
+        <v>financeiro@metalurgicapaulista.com.br</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -508,6 +515,9 @@
       <c r="J3" t="str">
         <v>SP</v>
       </c>
+      <c r="K3" t="str">
+        <v xml:space="preserve"> Compras@MercadoBomPreco.com.br </v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -540,6 +550,9 @@
       <c r="J4" t="str">
         <v>sp</v>
       </c>
+      <c r="K4" t="str">
+        <v>contato@clinicavida.com.br</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -636,6 +649,9 @@
       <c r="J7" t="str">
         <v>SP</v>
       </c>
+      <c r="K7" t="str">
+        <v>contato@</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -668,6 +684,9 @@
       <c r="J8" t="str">
         <v>SP</v>
       </c>
+      <c r="K8" t="str">
+        <v>padaria.central@gmail</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -700,6 +719,9 @@
       <c r="J9" t="str">
         <v>SP</v>
       </c>
+      <c r="K9" t="str">
+        <v>compras@mercadobompreco.com.br</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -732,6 +754,9 @@
       <c r="J10" t="str">
         <v>SP</v>
       </c>
+      <c r="K10" t="str">
+        <v>ti@saolucas.org.br</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -796,6 +821,9 @@
       <c r="J12" t="str">
         <v/>
       </c>
+      <c r="K12" t="str">
+        <v>financeiro textil@aurora.com.br</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -927,7 +955,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
   </ignoredErrors>
 </worksheet>
 </file>